--- a/survey_templates/049_guilt_and_well_being_survey--survey_templates.xlsx
+++ b/survey_templates/049_guilt_and_well_being_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A brief overview of the survey and its purpose.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_is_guilt</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is guilt?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please describe your understanding of guilt.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>how_does_guilt_affect</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How does guilt affect you?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How do you typically respond to feelings of guilt?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_does_it_affect</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you experience guilt?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10, how often do you feel guilty?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -617,10 +633,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>frequency_of_guilt</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Intensity of guilt</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>On a scale of 1-10, how intense is your guilt?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -640,10 +660,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>intensity_of_guilt</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How does it affect you?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How do you think guilt affects you emotionally?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,23 +677,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question6</t>
+          <t>question8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>how_does_it_affect</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Coping strategies</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Choose one or more from the list below</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question7</t>
+          <t>question9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>emotional_expression</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Emotional Expression</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How do you express your emotions in response to guilt?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,46 +731,54 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question8</t>
+          <t>question10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>coping_strategies</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Emotional state</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How do you feel when experiencing guilt?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question8</t>
+          <t>question11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>emotional_state</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Question11</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Choose one or more from the list below</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question9</t>
+          <t>question12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>emotional_expression</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Question12</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How do you express your emotions in response to guilt?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question10</t>
+          <t>question13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>how_do_people</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Question13</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>How do you feel when experiencing guilt?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question10</t>
+          <t>question14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>emotional_state</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>How do people respond to guilt?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>How do people typically respond to feelings of guilt?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,46 +866,54 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question11</t>
+          <t>question15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>coping_strategies</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Question15</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>How do you feel when experiencing guilt?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question12</t>
+          <t>question16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>emotional_expression</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Question16</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Choose one or more from the list below</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question13</t>
+          <t>question17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>emotional_state</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Question17</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>How do you express your emotions in response to guilt?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question14</t>
+          <t>question17_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>how_do_people</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Question17 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>How do you feel when experiencing guilt?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question14</t>
+          <t>question18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>emotional_state</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Question18</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How do people typically respond to feelings of guilt?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -934,15 +1006,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>question15</t>
+          <t>question19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>coping_strategies</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Question19</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Choose one or more from the list below</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>yes</t>
@@ -957,15 +1033,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question16</t>
+          <t>question20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>emotional_expression</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Question20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>How do you express your emotions in response to guilt?</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -983,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1079,17 +1159,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question11_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>guilt</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guilt</t>
+          <t>Fear</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1181,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>shame</t>
+          <t>guilt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shame</t>
+          <t>Guilt</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1198,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pride</t>
+          <t>shame</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pride</t>
+          <t>Shame</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1215,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>pride</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Anger</t>
+          <t>Pride</t>
         </is>
       </c>
     </row>
@@ -1152,95 +1232,197 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>Anger</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question11_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>guilt</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Guilt</t>
+          <t>Fear</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shame</t>
+          <t>guilt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shame</t>
+          <t>Guilt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pride</t>
+          <t>shame</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pride</t>
+          <t>Shame</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>pride</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Anger</t>
+          <t>Pride</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question15_choices</t>
+          <t>question16_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>anger</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Anger</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>question16_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>question19_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>guilt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Guilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question19_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>shame</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Shame</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question19_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pride</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pride</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question19_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>anger</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Anger</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question19_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Fear</t>
         </is>
